--- a/leads_dentista_curitiba.xlsx
+++ b/leads_dentista_curitiba.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALE A PENA ASSISTIR Odontologia Curitiba Den</t>
+          <t>Vale a Pena Assistir Odontologia Curitib</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,10 +529,8 @@
           <t>(41) 98825-8833</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5541988258833</t>
-        </is>
+      <c r="I2" t="n">
+        <v>5541988258833</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -607,10 +605,8 @@
           <t>(41) 98497-9594</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5541984979594</t>
-        </is>
+      <c r="I3" t="n">
+        <v>5541984979594</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -685,10 +681,8 @@
           <t>(41) 3095-6347</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>554130956347</t>
-        </is>
+      <c r="I4" t="n">
+        <v>554130956347</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -725,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Odontologias / Dentistas</t>
+          <t>Odontologias</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -837,10 +831,8 @@
           <t>(41) 99677-0006</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5541996770006</t>
-        </is>
+      <c r="I6" t="n">
+        <v>5541996770006</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -877,7 +869,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dentistas Curitiba</t>
+          <t>Dentistas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -915,10 +907,8 @@
           <t>(41) 3224-4554</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>554132244554</t>
-        </is>
+      <c r="I7" t="n">
+        <v>554132244554</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -993,10 +983,8 @@
           <t>(41) 3253-1907</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>554132531907</t>
-        </is>
+      <c r="I8" t="n">
+        <v>554132531907</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1107,7 +1095,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Link To Facebook.com</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1255,7 +1243,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Odonto Pio XII</t>
+          <t>Odonto Pio Xii</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1293,10 +1281,8 @@
           <t>(41) 3232-6195</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>554132326195</t>
-        </is>
+      <c r="I12" t="n">
+        <v>554132326195</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1371,10 +1357,8 @@
           <t>(41) 98868-8164</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5541988688164</t>
-        </is>
+      <c r="I13" t="n">
+        <v>5541988688164</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1449,10 +1433,8 @@
           <t>(41) 98868-8164</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5541988688164</t>
-        </is>
+      <c r="I14" t="n">
+        <v>5541988688164</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1527,10 +1509,8 @@
           <t>(41) 98444-8862</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5541984448862</t>
-        </is>
+      <c r="I15" t="n">
+        <v>5541984448862</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1567,7 +1547,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Clnica Odontolgica Curitiba Instituto Kopp Od</t>
+          <t>Clnica Odontolgica Curitiba Instituto Ko</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1605,10 +1585,8 @@
           <t>(41) 3363-7295</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>554133637295</t>
-        </is>
+      <c r="I16" t="n">
+        <v>554133637295</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1941,7 +1919,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LiveDent</t>
+          <t>Livedent</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1979,10 +1957,8 @@
           <t>41302485</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5541302485</t>
-        </is>
+      <c r="I21" t="n">
+        <v>5541302485</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2019,7 +1995,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maxiclin Odontologia Curitiba</t>
+          <t>Maxiclin Odontologia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2057,10 +2033,8 @@
           <t>(41) 98519-4512</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5541985194512</t>
-        </is>
+      <c r="I22" t="n">
+        <v>5541985194512</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2097,7 +2071,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10 MELHORES Clnicas Odontolgicas</t>
+          <t>10 Melhores Clnicas Odontolgicas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2171,7 +2145,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dental Uni 24H, R. Silveira Peixoto, 1040</t>
+          <t>Dental Uni 24h, R. Silveira Peixoto, 104</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2209,10 +2183,8 @@
           <t>(41) 3342-9060</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>554133429060</t>
-        </is>
+      <c r="I24" t="n">
+        <v>554133429060</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2249,7 +2221,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dentistas, Clnicas Odontolgicas na Cidade de</t>
+          <t>Dentistas, Clnicas Odontolgicas Na Cidad</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2333,8 @@
           <t>(41) 3027-7200</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>554130277200</t>
-        </is>
+      <c r="I26" t="n">
+        <v>554130277200</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2439,10 +2409,8 @@
           <t>(41) 3264-1984</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>554132641984</t>
-        </is>
+      <c r="I27" t="n">
+        <v>554132641984</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2479,7 +2447,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Oralclin clnica odontolgica localizada</t>
+          <t>Oralclin Clnica Odontolgica Localizada</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2517,10 +2485,8 @@
           <t>41334531</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5541334531</t>
-        </is>
+      <c r="I28" t="n">
+        <v>5541334531</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2557,7 +2523,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Curitiba</t>
+          <t>10 Melhores Dentistas para</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2631,7 +2597,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dentista Curitiba</t>
+          <t>Dentista</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2669,10 +2635,8 @@
           <t>(41) 98798-1235</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5541987981235</t>
-        </is>
+      <c r="I30" t="n">
+        <v>5541987981235</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2747,10 +2711,8 @@
           <t>(41) 99257-8253</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5541992578253</t>
-        </is>
+      <c r="I31" t="n">
+        <v>5541992578253</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2825,10 +2787,8 @@
           <t>(41) 3362-1721</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>554133621721</t>
-        </is>
+      <c r="I32" t="n">
+        <v>554133621721</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2903,10 +2863,8 @@
           <t>(41) 3257-1026</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>554132571026</t>
-        </is>
+      <c r="I33" t="n">
+        <v>554132571026</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3055,10 +3013,8 @@
           <t>(41) 99199-3627</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5541991993627</t>
-        </is>
+      <c r="I35" t="n">
+        <v>5541991993627</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3095,7 +3051,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Melhor dentista</t>
+          <t>Melhor Dentista</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3133,10 +3089,8 @@
           <t>(41) 98825-8833</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5541988258833</t>
-        </is>
+      <c r="I36" t="n">
+        <v>5541988258833</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3247,7 +3201,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VITAL SMILE</t>
+          <t>Vital Smile</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3285,10 +3239,8 @@
           <t>41998023</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5541998023</t>
-        </is>
+      <c r="I38" t="n">
+        <v>5541998023</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
